--- a/Fourth Semester/static and probability/lab8-not done yet/LAB8 (assignment).xlsx
+++ b/Fourth Semester/static and probability/lab8-not done yet/LAB8 (assignment).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ACER-WIN10\Documents\GitHub\BCE\Fourth Semester\static and probability\lab8-not done yet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67AB1133-8094-4677-9AD4-C6945D34465C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D63BE7E0-950F-438D-BA1E-230487C43F1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="21840" windowHeight="13290" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1007,7 +1007,7 @@
         <v>165.35615955760434</v>
       </c>
       <c r="E24">
-        <f t="shared" ref="E23:F30" si="1">ROUND(C24,0)</f>
+        <f t="shared" ref="E24:E30" si="1">ROUND(C24,0)</f>
         <v>165</v>
       </c>
     </row>
@@ -1246,6 +1246,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
